--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487064_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487064_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.75</v>
+        <v>8.0831</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9354</v>
+        <v>7.2953</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8146</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>3.3097</v>
@@ -610,13 +610,13 @@
         <v>3.2811</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.626</v>
+        <v>-0.2928</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3886</v>
+        <v>-0.0287</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2373</v>
+        <v>-0.2641</v>
       </c>
       <c r="V2" t="n">
         <v>2.9432</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. JORGE RODRIGUEZ</t>
+          <t>F. AMBROSONI ÁLVAREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0905</v>
+        <v>4.8435</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3572</v>
+        <v>4.0991</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2667</v>
+        <v>0.7443</v>
       </c>
       <c r="G3" t="n">
-        <v>7.1767</v>
+        <v>1.1479</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1981</v>
+        <v>1.1157</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9785</v>
+        <v>0.0321</v>
       </c>
       <c r="J3" t="n">
-        <v>7.0765</v>
+        <v>0.6733</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8862</v>
+        <v>0.7554</v>
       </c>
       <c r="L3" t="n">
-        <v>3.1903</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1002</v>
+        <v>0.4745</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6881</v>
+        <v>0.3603</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7883</v>
+        <v>0.1142</v>
       </c>
       <c r="P3" t="n">
-        <v>0.579</v>
+        <v>1.5441</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3161</v>
+        <v>-0.386</v>
       </c>
       <c r="R3" t="n">
-        <v>2.8951</v>
+        <v>1.9301</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9234</v>
+        <v>-0.3044</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4032</v>
+        <v>-0.158</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5202</v>
+        <v>-0.1464</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.7418</v>
+        <v>2.4559</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.9698</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.7418</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. AMBROSONI ÁLVAREZ</t>
+          <t>J. JORGE RODRIGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9482</v>
+        <v>4.732</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4983</v>
+        <v>4.7578</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4499</v>
+        <v>-0.0258</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1479</v>
+        <v>7.1767</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1157</v>
+        <v>3.1981</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0321</v>
+        <v>3.9785</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6733</v>
+        <v>7.0765</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7554</v>
+        <v>3.8862</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.08210000000000001</v>
+        <v>3.1903</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4745</v>
+        <v>0.1002</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3603</v>
+        <v>-0.6881</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1142</v>
+        <v>0.7883</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5441</v>
+        <v>0.579</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.386</v>
+        <v>-2.3161</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9301</v>
+        <v>2.8951</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1997</v>
+        <v>-0.2819</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7588</v>
+        <v>-0.0026</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4409</v>
+        <v>-0.2793</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4559</v>
+        <v>-2.7418</v>
       </c>
       <c r="W4" t="n">
-        <v>3.9698</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.5138</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. REY GUTIERREZ</t>
+          <t>A. GARCIA NAVALON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1</v>
+        <v>2.9134</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2303</v>
+        <v>2.8989</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1303</v>
+        <v>0.0144</v>
       </c>
       <c r="G5" t="n">
-        <v>1.539</v>
+        <v>-2.4594</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.7737</v>
+        <v>-3.0698</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3127</v>
+        <v>0.6105</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2416</v>
+        <v>-0.8838</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5434</v>
+        <v>-0.9731</v>
       </c>
       <c r="L5" t="n">
-        <v>3.785</v>
+        <v>0.0893</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7026</v>
+        <v>-1.5755</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.2303</v>
+        <v>-2.0968</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.5212</v>
       </c>
       <c r="P5" t="n">
-        <v>0.193</v>
+        <v>1.3511</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.158</v>
+        <v>1.3511</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2882</v>
+        <v>0.3378</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0462</v>
+        <v>0.0988</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2419</v>
+        <v>0.2389</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6562</v>
+        <v>3.6839</v>
       </c>
       <c r="W5" t="n">
+        <v>3.6839</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.6562</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. REYES ABAD</t>
+          <t>A. REY GUTIERREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8344</v>
+        <v>1.984</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0486</v>
+        <v>2.1679</v>
       </c>
       <c r="F6" t="n">
-        <v>2.883</v>
+        <v>-0.1838</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4656</v>
+        <v>1.539</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4697</v>
+        <v>-2.7737</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9353</v>
+        <v>4.3127</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6529</v>
+        <v>3.2416</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1799</v>
+        <v>-0.5434</v>
       </c>
       <c r="L6" t="n">
-        <v>1.473</v>
+        <v>3.785</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1873</v>
+        <v>-1.7026</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.6496</v>
+        <v>-2.2303</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4623</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.8951</v>
+        <v>0.193</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.7902</v>
+        <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>2.8951</v>
+        <v>1.158</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8356</v>
+        <v>-0.4042</v>
       </c>
       <c r="T6" t="n">
-        <v>2.0888</v>
+        <v>-0.1087</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7469</v>
+        <v>-0.2955</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5717</v>
+        <v>0.6562</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5717</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GARCIA NAVALON</t>
+          <t>N. NDOYE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8267</v>
+        <v>0.8806</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1603</v>
+        <v>0.1046</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3336</v>
+        <v>0.776</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.4594</v>
+        <v>0.2629</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.0698</v>
+        <v>-0.0041</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6105</v>
+        <v>0.267</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8838</v>
+        <v>0.0828</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9731</v>
+        <v>0.0828</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0893</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5755</v>
+        <v>0.1801</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.0968</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5212</v>
+        <v>0.267</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7489</v>
+        <v>-0.2895</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6398</v>
+        <v>0.0218</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1091</v>
+        <v>-0.3113</v>
       </c>
       <c r="V7" t="n">
-        <v>3.6839</v>
+        <v>0.3281</v>
       </c>
       <c r="W7" t="n">
-        <v>3.6839</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1724</v>
+        <v>0.5081</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8057</v>
+        <v>-2.0684</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9781</v>
+        <v>2.5765</v>
       </c>
       <c r="G8" t="n">
         <v>-1.6305</v>
@@ -1078,13 +1078,13 @@
         <v>2.1231</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3517</v>
+        <v>0.6874</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3385</v>
+        <v>0.0757</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0132</v>
+        <v>0.6117</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2859</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. NDOYE</t>
+          <t>A. REYES ABAD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6268</v>
+        <v>-0.0246</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-2.3722</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7224</v>
+        <v>2.3476</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2629</v>
+        <v>2.4656</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0041</v>
+        <v>-0.4697</v>
       </c>
       <c r="I9" t="n">
-        <v>0.267</v>
+        <v>2.9353</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0828</v>
+        <v>2.6529</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0828</v>
+        <v>1.1799</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.473</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1801</v>
+        <v>-0.1873</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-1.6496</v>
       </c>
       <c r="O9" t="n">
-        <v>0.267</v>
+        <v>1.4623</v>
       </c>
       <c r="P9" t="n">
-        <v>0.579</v>
+        <v>-2.8951</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-5.7902</v>
       </c>
       <c r="R9" t="n">
-        <v>0.579</v>
+        <v>2.8951</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5433</v>
+        <v>0.9766</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1785</v>
+        <v>0.7651</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3649</v>
+        <v>0.2115</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3281</v>
+        <v>-0.5717</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3281</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8002</v>
+        <v>-2.4621</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5873</v>
+        <v>-2.2492</v>
       </c>
       <c r="F10" t="n">
         <v>-0.2129</v>
@@ -1234,10 +1234,10 @@
         <v>1.7371</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1335</v>
+        <v>0.2046</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1507</v>
+        <v>0.1874</v>
       </c>
       <c r="U10" t="n">
         <v>0.0172</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0739</v>
+        <v>-2.7933</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7163</v>
+        <v>-1.516</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3576</v>
+        <v>-1.2773</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8171</v>
@@ -1312,13 +1312,13 @@
         <v>0.386</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.392</v>
+        <v>-0.1114</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4759</v>
+        <v>-0.2756</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0839</v>
+        <v>0.1642</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8999</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>17.4749</v>
+        <v>18.6647</v>
       </c>
       <c r="E12" t="n">
-        <v>11.9279</v>
+        <v>13.1178</v>
       </c>
       <c r="F12" t="n">
-        <v>5.5469</v>
+        <v>5.546799999999998</v>
       </c>
       <c r="G12" t="n">
-        <v>8.035</v>
+        <v>8.034999999999998</v>
       </c>
       <c r="H12" t="n">
         <v>-8.8802</v>
@@ -1366,7 +1366,7 @@
         <v>13.9424</v>
       </c>
       <c r="K12" t="n">
-        <v>2.239499999999999</v>
+        <v>2.2395</v>
       </c>
       <c r="L12" t="n">
         <v>11.703</v>
@@ -1378,10 +1378,10 @@
         <v>-11.1197</v>
       </c>
       <c r="O12" t="n">
-        <v>5.2123</v>
+        <v>5.212300000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>4.825299999999999</v>
+        <v>4.825300000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.5104</v>
@@ -1390,13 +1390,13 @@
         <v>18.3357</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6677000000000004</v>
+        <v>0.5222000000000002</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6144000000000001</v>
+        <v>0.5751999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0530999999999999</v>
+        <v>-0.05309999999999993</v>
       </c>
       <c r="V12" t="n">
         <v>5.282100000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.0303</v>
+        <v>2.7995</v>
       </c>
       <c r="E13" t="n">
-        <v>7.6666</v>
+        <v>5.864</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6362</v>
+        <v>-3.0645</v>
       </c>
       <c r="G13" t="n">
         <v>3.3024</v>
@@ -1468,13 +1468,13 @@
         <v>1.3511</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3962</v>
+        <v>1.1653</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3267</v>
+        <v>0.5242</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0694</v>
+        <v>0.6411</v>
       </c>
       <c r="V13" t="n">
         <v>-2.8263</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. ARTECHE URRUZOLA</t>
+          <t>E. ANDRES CAMPOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,31 +1501,31 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8975</v>
+        <v>1.7087</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9839</v>
+        <v>1.9397</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.2309</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5112</v>
+        <v>0.5004</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3041</v>
+        <v>0.5218</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2071</v>
+        <v>-0.0214</v>
       </c>
       <c r="J14" t="n">
-        <v>2.046</v>
+        <v>2.0352</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2727</v>
+        <v>1.4903</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7733</v>
+        <v>0.5448</v>
       </c>
       <c r="M14" t="n">
         <v>-1.5348</v>
@@ -1537,37 +1537,37 @@
         <v>-0.5662</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.158</v>
+        <v>1.7371</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.8951</v>
+        <v>-0.193</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>3.8146</v>
+        <v>-0.2006</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8754</v>
+        <v>-0.1883</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9392</v>
+        <v>-0.0123</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2702</v>
+        <v>-0.3281</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.0422</v>
+        <v>0.2859</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.228</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. ANDRES CAMPOS</t>
+          <t>I. SAGASTI ARGOTE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.547</v>
+        <v>-0.0528</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9383</v>
+        <v>-0.0388</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3912</v>
+        <v>-0.014</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5004</v>
+        <v>-0.0528</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5218</v>
+        <v>-0.0528</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0214</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0352</v>
+        <v>0.0207</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4903</v>
+        <v>0.0207</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5448</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5348</v>
+        <v>-0.0735</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9685</v>
+        <v>-0.0735</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5662</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7371</v>
+        <v>0.193</v>
       </c>
       <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="S15" t="n">
         <v>-0.193</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.9301</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-1.3623</v>
-      </c>
       <c r="T15" t="n">
-        <v>-1.1898</v>
+        <v>-0.0595</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1725</v>
+        <v>-0.1335</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3281</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. SAGASTI ARGOTE</t>
+          <t>I. ARTECHE URRUZOLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0528</v>
+        <v>-0.1731</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0388</v>
+        <v>0.1814</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.014</v>
+        <v>-0.3545</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0528</v>
+        <v>0.5112</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0528</v>
+        <v>0.3041</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.2071</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0207</v>
+        <v>2.046</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0207</v>
+        <v>1.2727</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.7733</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0735</v>
+        <v>-1.5348</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0735</v>
+        <v>-0.9685</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.5662</v>
       </c>
       <c r="P16" t="n">
-        <v>0.193</v>
+        <v>-1.158</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R16" t="n">
-        <v>0.193</v>
+        <v>1.7371</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.193</v>
+        <v>1.744</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0595</v>
+        <v>1.0728</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1335</v>
+        <v>0.6712</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.2702</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.0422</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.626</v>
+        <v>-0.2582</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3476</v>
+        <v>0.4478</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9737</v>
+        <v>-0.706</v>
       </c>
       <c r="G17" t="n">
         <v>0.497</v>
@@ -1780,13 +1780,13 @@
         <v>1.3511</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.965</v>
+        <v>-0.5972</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6544</v>
+        <v>-0.5542</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3107</v>
+        <v>-0.043</v>
       </c>
       <c r="V17" t="n">
         <v>0.614</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9182</v>
+        <v>-1.7109</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6031</v>
+        <v>-0.503</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3151</v>
+        <v>-1.208</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7793</v>
@@ -1858,13 +1858,13 @@
         <v>0.386</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7601</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4164</v>
+        <v>-0.3163</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3437</v>
+        <v>-0.2366</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5717</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6175</v>
+        <v>-2.4777</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2468</v>
+        <v>-0.9464</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3707</v>
+        <v>-1.5313</v>
       </c>
       <c r="G19" t="n">
         <v>0.3125</v>
@@ -1936,13 +1936,13 @@
         <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0277</v>
+        <v>0.1676</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4759</v>
+        <v>-0.1755</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5037</v>
+        <v>0.343</v>
       </c>
       <c r="V19" t="n">
         <v>-1.7997</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4722</v>
+        <v>-3.0112</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.7665</v>
+        <v>-3.4661</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2943</v>
+        <v>0.4549</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2981</v>
@@ -2014,13 +2014,13 @@
         <v>0.965</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.051</v>
+        <v>-0.5899</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8328</v>
+        <v>-0.5324</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2181</v>
+        <v>-0.0575</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8779</v>
+        <v>-3.6571</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9538</v>
+        <v>-1.054</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9241</v>
+        <v>-2.6032</v>
       </c>
       <c r="G21" t="n">
         <v>-3.219</v>
@@ -2092,13 +2092,13 @@
         <v>1.5441</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.009900000000000001</v>
+        <v>0.2109</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5024</v>
+        <v>0.4022</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5123</v>
+        <v>-0.1914</v>
       </c>
       <c r="V21" t="n">
         <v>-1.228</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.5441</v>
+        <v>-4.4359</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3852</v>
+        <v>-3.3838</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1589</v>
+        <v>-1.0521</v>
       </c>
       <c r="G22" t="n">
         <v>-5.3438</v>
@@ -2170,13 +2170,13 @@
         <v>1.7371</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.819</v>
+        <v>0.2892</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9518</v>
+        <v>0.0496</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1328</v>
+        <v>0.2396</v>
       </c>
       <c r="V22" t="n">
         <v>2.7418</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.8409</v>
+        <v>-5.5385</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.4889</v>
+        <v>-4.5877</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.352</v>
+        <v>-0.9508</v>
       </c>
       <c r="G23" t="n">
         <v>-3.4654</v>
@@ -2248,13 +2248,13 @@
         <v>1.5441</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4105</v>
+        <v>-0.1081</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0708</v>
+        <v>-0.1695</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3398</v>
+        <v>0.0614</v>
       </c>
       <c r="V23" t="n">
         <v>-0.614</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-17.4748</v>
+        <v>-16.8072</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.546700000000001</v>
+        <v>-5.5469</v>
       </c>
       <c r="F24" t="n">
-        <v>-11.9281</v>
+        <v>-11.2604</v>
       </c>
       <c r="G24" t="n">
         <v>-8.0349</v>
@@ -2326,13 +2326,13 @@
         <v>13.5107</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6677000000000002</v>
+        <v>1.3353</v>
       </c>
       <c r="T24" t="n">
-        <v>0.05309999999999948</v>
+        <v>0.05310000000000015</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6145000000000002</v>
+        <v>1.282</v>
       </c>
       <c r="V24" t="n">
         <v>-5.2822</v>
